--- a/demo_data/sample_inventory.xlsx
+++ b/demo_data/sample_inventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="15">
   <si>
     <t>Ürün</t>
   </si>
@@ -46,10 +46,19 @@
     <t>Ürün D</t>
   </si>
   <si>
+    <t>Ürün E</t>
+  </si>
+  <si>
+    <t>Ürün F</t>
+  </si>
+  <si>
     <t>Merkez Depo</t>
   </si>
   <si>
     <t>İstanbul Depo</t>
+  </si>
+  <si>
+    <t>Anadolu Depo</t>
   </si>
 </sst>
 </file>
@@ -57,10 +66,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -76,7 +93,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,12 +101,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -385,26 +420,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -413,19 +448,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>2935</v>
+        <v>648</v>
       </c>
       <c r="D2">
-        <v>66</v>
+        <v>102.32</v>
       </c>
       <c r="E2">
-        <v>193710</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46017</v>
+        <v>36530</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46022</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -433,39 +468,39 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>3036</v>
+        <v>2650</v>
       </c>
       <c r="D3">
-        <v>66</v>
+        <v>100.65</v>
       </c>
       <c r="E3">
-        <v>200376</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46017</v>
+        <v>146952</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45994</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>2217</v>
+        <v>2024</v>
       </c>
       <c r="D4">
-        <v>46.75</v>
+        <v>102.97</v>
       </c>
       <c r="E4">
-        <v>103645</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45842</v>
+        <v>114825</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46000</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -473,39 +508,39 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>2890</v>
+        <v>2498</v>
       </c>
       <c r="D5">
-        <v>46.75</v>
+        <v>57.08</v>
       </c>
       <c r="E5">
-        <v>135108</v>
-      </c>
-      <c r="F5" s="1">
-        <v>45932</v>
+        <v>78558</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45994</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>2641</v>
+        <v>3132</v>
       </c>
       <c r="D6">
-        <v>115.5</v>
+        <v>57.92</v>
       </c>
       <c r="E6">
-        <v>305036</v>
-      </c>
-      <c r="F6" s="1">
-        <v>45997</v>
+        <v>99946</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46012</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -513,59 +548,199 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>1568</v>
+        <v>2487</v>
       </c>
       <c r="D7">
-        <v>115.5</v>
+        <v>141.7</v>
       </c>
       <c r="E7">
-        <v>181104</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46012</v>
+        <v>194161</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45968</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8">
-        <v>3243</v>
+        <v>935</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>138.4</v>
       </c>
       <c r="E8">
-        <v>107019</v>
-      </c>
-      <c r="F8" s="1">
-        <v>45842</v>
+        <v>71296</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46011</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>2842</v>
+      </c>
+      <c r="D9">
+        <v>144.6</v>
+      </c>
+      <c r="E9">
+        <v>226417</v>
+      </c>
+      <c r="F9" s="2">
+        <v>45916</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>2970</v>
+      </c>
+      <c r="D10">
+        <v>40.6</v>
+      </c>
+      <c r="E10">
+        <v>66435</v>
+      </c>
+      <c r="F10" s="2">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>2437</v>
+      </c>
+      <c r="D11">
+        <v>40.67</v>
+      </c>
+      <c r="E11">
+        <v>54607</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1648</v>
+      </c>
+      <c r="D12">
+        <v>227.3</v>
+      </c>
+      <c r="E12">
+        <v>206383</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>2457</v>
+      </c>
+      <c r="D13">
+        <v>228.46</v>
+      </c>
+      <c r="E13">
+        <v>309266</v>
+      </c>
+      <c r="F13" s="2">
+        <v>45900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>1918</v>
+      </c>
+      <c r="D14">
+        <v>225.32</v>
+      </c>
+      <c r="E14">
+        <v>238103</v>
+      </c>
+      <c r="F14" s="2">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="C9">
-        <v>1786</v>
-      </c>
-      <c r="D9">
-        <v>33</v>
-      </c>
-      <c r="E9">
-        <v>58938</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46012</v>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1916</v>
+      </c>
+      <c r="D15">
+        <v>31.41</v>
+      </c>
+      <c r="E15">
+        <v>33157</v>
+      </c>
+      <c r="F15" s="2">
+        <v>45818</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>1389</v>
+      </c>
+      <c r="D16">
+        <v>30.53</v>
+      </c>
+      <c r="E16">
+        <v>23364</v>
+      </c>
+      <c r="F16" s="2">
+        <v>45978</v>
       </c>
     </row>
   </sheetData>
